--- a/src_code/outputs/SC3_salonly_results.xlsx
+++ b/src_code/outputs/SC3_salonly_results.xlsx
@@ -506,22 +506,22 @@
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3465</v>
+        <v>0.3481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2105</v>
+        <v>0.2214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.506</v>
+        <v>0.5014</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3029</v>
+        <v>0.2971</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2248</v>
+        <v>0.2225</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8329</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="3">
@@ -552,22 +552,22 @@
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3122</v>
+        <v>0.3167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1959</v>
+        <v>0.1986</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5976</v>
+        <v>0.5858</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3054</v>
+        <v>0.2897</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2335</v>
+        <v>0.2168</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8297</v>
+        <v>0.8468</v>
       </c>
     </row>
     <row r="4">
@@ -598,22 +598,22 @@
         <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3341</v>
+        <v>0.335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2096</v>
+        <v>0.2127</v>
       </c>
       <c r="I4" t="n">
-        <v>0.536</v>
+        <v>0.5336</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3427</v>
+        <v>0.3292</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2589</v>
+        <v>0.2486</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7845</v>
+        <v>0.8012</v>
       </c>
     </row>
     <row r="5">
@@ -644,22 +644,22 @@
         <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3129</v>
+        <v>0.3142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1956</v>
+        <v>0.1959</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.5927</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2716</v>
+        <v>0.268</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1997</v>
+        <v>0.1969</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="6">
@@ -690,22 +690,22 @@
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2695</v>
+        <v>0.2681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1723</v>
+        <v>0.1637</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6995</v>
+        <v>0.7024</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2609</v>
+        <v>0.255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.197</v>
+        <v>0.1891</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8756</v>
+        <v>0.8811</v>
       </c>
     </row>
     <row r="7">
@@ -736,22 +736,22 @@
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3081</v>
+        <v>0.3073</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1917</v>
+        <v>0.1943</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6045</v>
+        <v>0.6065</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3152</v>
+        <v>0.3212</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2363</v>
+        <v>0.242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8174</v>
+        <v>0.8104</v>
       </c>
     </row>
     <row r="8">
@@ -782,22 +782,22 @@
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.201</v>
+        <v>0.2014</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1307</v>
+        <v>0.1311</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8325</v>
+        <v>0.8318</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2192</v>
+        <v>0.2171</v>
       </c>
       <c r="K8" t="n">
-        <v>0.161</v>
+        <v>0.1609</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9121</v>
+        <v>0.9139</v>
       </c>
     </row>
     <row r="9">
@@ -828,22 +828,22 @@
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2064</v>
+        <v>0.2071</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1312</v>
+        <v>0.1323</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8227</v>
+        <v>0.8215</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2442</v>
+        <v>0.2319</v>
       </c>
       <c r="K9" t="n">
-        <v>0.179</v>
+        <v>0.1716</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8907</v>
+        <v>0.9015</v>
       </c>
     </row>
     <row r="10">
@@ -874,22 +874,22 @@
         <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2672</v>
+        <v>0.2648</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1734</v>
+        <v>0.1659</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7008</v>
+        <v>0.7063</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3739</v>
+        <v>0.3892</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2671</v>
+        <v>0.2643</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7209</v>
       </c>
     </row>
     <row r="11">
@@ -920,22 +920,22 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1884</v>
+        <v>0.193</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1211</v>
+        <v>0.1296</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8514</v>
+        <v>0.8439</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2079</v>
+        <v>0.2095</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1514</v>
+        <v>0.1547</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9206</v>
+        <v>0.9193</v>
       </c>
     </row>
     <row r="12">
@@ -966,22 +966,22 @@
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1983</v>
+        <v>0.2018</v>
       </c>
       <c r="H12" t="n">
-        <v>0.128</v>
+        <v>0.1265</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8347</v>
+        <v>0.8289</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2261</v>
+        <v>0.2247</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1652</v>
+        <v>0.1634</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9058</v>
+        <v>0.9069</v>
       </c>
     </row>
     <row r="13">
@@ -1012,22 +1012,22 @@
         <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>0.258</v>
+        <v>0.2546</v>
       </c>
       <c r="H13" t="n">
-        <v>0.165</v>
+        <v>0.1587</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7257</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3163</v>
+        <v>0.3196</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2298</v>
+        <v>0.2297</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8147</v>
+        <v>0.8107</v>
       </c>
     </row>
     <row r="14">
@@ -1058,22 +1058,22 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3483</v>
+        <v>0.3524</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2192</v>
+        <v>0.2225</v>
       </c>
       <c r="I14" t="n">
-        <v>0.501</v>
+        <v>0.4892</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3031</v>
+        <v>0.307</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2306</v>
+        <v>0.2329</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8327</v>
+        <v>0.8283</v>
       </c>
     </row>
     <row r="15">
@@ -1104,22 +1104,22 @@
         <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3188</v>
+        <v>0.3206</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1974</v>
+        <v>0.1978</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5804</v>
+        <v>0.5757</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2948</v>
+        <v>0.298</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2218</v>
+        <v>0.2234</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8414</v>
+        <v>0.8379</v>
       </c>
     </row>
     <row r="16">
@@ -1150,22 +1150,22 @@
         <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3438</v>
+        <v>0.3397</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2156</v>
+        <v>0.2125</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5088</v>
+        <v>0.5206</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3528</v>
+        <v>0.3725</v>
       </c>
       <c r="K16" t="n">
-        <v>0.269</v>
+        <v>0.2768</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7715</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="17">
@@ -1196,22 +1196,22 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3383</v>
+        <v>0.3369</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2115</v>
+        <v>0.2127</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5279</v>
+        <v>0.5319</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2863</v>
+        <v>0.2786</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2197</v>
+        <v>0.2076</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8505</v>
+        <v>0.8585</v>
       </c>
     </row>
     <row r="18">
@@ -1242,22 +1242,22 @@
         <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2849</v>
+        <v>0.2906</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1737</v>
+        <v>0.1778</v>
       </c>
       <c r="I18" t="n">
-        <v>0.664</v>
+        <v>0.6505</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2869</v>
+        <v>0.2709</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2132</v>
+        <v>0.204</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8495</v>
+        <v>0.8659</v>
       </c>
     </row>
     <row r="19">
@@ -1288,22 +1288,22 @@
         <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3236</v>
+        <v>0.3243</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1966</v>
+        <v>0.2008</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5635</v>
+        <v>0.5617</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3844</v>
+        <v>0.3903</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2784</v>
+        <v>0.2843</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7284</v>
+        <v>0.7201</v>
       </c>
     </row>
     <row r="20">
@@ -1334,22 +1334,22 @@
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2249</v>
+        <v>0.2323</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1439</v>
+        <v>0.1499</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7903</v>
+        <v>0.7764</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2473</v>
+        <v>0.2336</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1817</v>
+        <v>0.1764</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8882</v>
+        <v>0.9002</v>
       </c>
     </row>
     <row r="21">
@@ -1380,22 +1380,22 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2253</v>
+        <v>0.2374</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1461</v>
+        <v>0.1418</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7889</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2542</v>
+        <v>0.2504</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1915</v>
+        <v>0.1828</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8851</v>
       </c>
     </row>
     <row r="22">
@@ -1426,22 +1426,22 @@
         <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2921</v>
+        <v>0.2796</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1951</v>
+        <v>0.1732</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6725</v>
       </c>
       <c r="J22" t="n">
-        <v>0.351</v>
+        <v>0.3854</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2668</v>
+        <v>0.2719</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7729</v>
+        <v>0.7262999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1472,22 +1472,22 @@
         <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1968</v>
+        <v>0.2133</v>
       </c>
       <c r="H23" t="n">
-        <v>0.127</v>
+        <v>0.1368</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8377</v>
+        <v>0.8095</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2453</v>
+        <v>0.2205</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1758</v>
+        <v>0.1611</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8894</v>
+        <v>0.9107</v>
       </c>
     </row>
     <row r="24">
@@ -1518,22 +1518,22 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2181</v>
+        <v>0.2201</v>
       </c>
       <c r="H24" t="n">
-        <v>0.138</v>
+        <v>0.1393</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.7963</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2425</v>
+        <v>0.2642</v>
       </c>
       <c r="K24" t="n">
-        <v>0.178</v>
+        <v>0.1845</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8917</v>
+        <v>0.8714</v>
       </c>
     </row>
     <row r="25">
@@ -1564,22 +1564,22 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2661</v>
+        <v>0.275</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1723</v>
+        <v>0.1734</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7002</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3973</v>
+        <v>0.3297</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2615</v>
+        <v>0.2396</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7075</v>
+        <v>0.7986</v>
       </c>
     </row>
     <row r="26">
@@ -1610,22 +1610,22 @@
         <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3477</v>
+        <v>0.3373</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2163</v>
+        <v>0.2144</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5026</v>
+        <v>0.5319</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2991</v>
+        <v>0.3204</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2266</v>
+        <v>0.2449</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8371</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1656,22 +1656,22 @@
         <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3195</v>
+        <v>0.317</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2005</v>
+        <v>0.1986</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5787</v>
+        <v>0.5851</v>
       </c>
       <c r="J27" t="n">
-        <v>0.293</v>
+        <v>0.2993</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2226</v>
+        <v>0.2292</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8365</v>
       </c>
     </row>
     <row r="28">
@@ -1702,22 +1702,22 @@
         <v>48</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3484</v>
+        <v>0.3498</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2227</v>
+        <v>0.2269</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4955</v>
+        <v>0.4915</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3527</v>
+        <v>0.3583</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2682</v>
+        <v>0.2762</v>
       </c>
       <c r="L28" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7644</v>
       </c>
     </row>
     <row r="29">
@@ -1748,22 +1748,22 @@
         <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3264</v>
+        <v>0.3288</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2048</v>
+        <v>0.2008</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5606</v>
+        <v>0.5541</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2723</v>
+        <v>0.2756</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2042</v>
+        <v>0.2047</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8648</v>
+        <v>0.8615</v>
       </c>
     </row>
     <row r="30">
@@ -1794,22 +1794,22 @@
         <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2797</v>
+        <v>0.2794</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1775</v>
+        <v>0.1686</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6762</v>
+        <v>0.6768</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2645</v>
+        <v>0.266</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2041</v>
+        <v>0.1993</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8721</v>
+        <v>0.8706</v>
       </c>
     </row>
     <row r="31">
@@ -1840,22 +1840,22 @@
         <v>48</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3209</v>
+        <v>0.3207</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1987</v>
+        <v>0.1967</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5709</v>
+        <v>0.5716</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3335</v>
+        <v>0.3398</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2505</v>
+        <v>0.2534</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7956</v>
+        <v>0.7877999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1886,22 +1886,22 @@
         <v>12</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2207</v>
+        <v>0.2178</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1474</v>
+        <v>0.1384</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7981</v>
+        <v>0.8034</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2478</v>
+        <v>0.235</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1842</v>
+        <v>0.173</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8878</v>
+        <v>0.8991</v>
       </c>
     </row>
     <row r="33">
@@ -1932,22 +1932,22 @@
         <v>24</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2295</v>
+        <v>0.2274</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1473</v>
+        <v>0.1502</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7809</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2479</v>
+        <v>0.2496</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1859</v>
+        <v>0.1896</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8874</v>
+        <v>0.8858</v>
       </c>
     </row>
     <row r="34">
@@ -1978,22 +1978,22 @@
         <v>48</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2833</v>
+        <v>0.2767</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1732</v>
+        <v>0.1679</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6793</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3617</v>
+        <v>0.3718</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2577</v>
+        <v>0.2606</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7589</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="35">
@@ -2024,19 +2024,19 @@
         <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2089</v>
+        <v>0.2027</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1352</v>
+        <v>0.1292</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8171</v>
+        <v>0.8278</v>
       </c>
       <c r="J35" t="n">
         <v>0.2307</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1687</v>
+        <v>0.1662</v>
       </c>
       <c r="L35" t="n">
         <v>0.9022</v>
@@ -2070,22 +2070,22 @@
         <v>24</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2129</v>
+        <v>0.2225</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1319</v>
+        <v>0.1433</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8093</v>
+        <v>0.7919</v>
       </c>
       <c r="J36" t="n">
-        <v>0.244</v>
+        <v>0.2451</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1748</v>
+        <v>0.1812</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8903</v>
+        <v>0.8893</v>
       </c>
     </row>
     <row r="37">
@@ -2116,22 +2116,22 @@
         <v>48</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2695</v>
+        <v>0.2713</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1642</v>
+        <v>0.1687</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6925</v>
+        <v>0.6884</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3567</v>
+        <v>0.3539</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2495</v>
+        <v>0.2496</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7642</v>
+        <v>0.7679</v>
       </c>
     </row>
     <row r="38">
@@ -2162,22 +2162,22 @@
         <v>12</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3395</v>
+        <v>0.3462</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2186</v>
+        <v>0.2141</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5259</v>
+        <v>0.5069</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3375</v>
+        <v>0.3401</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2564</v>
+        <v>0.2527</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7925</v>
+        <v>0.7893</v>
       </c>
     </row>
     <row r="39">
@@ -2208,22 +2208,22 @@
         <v>24</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3195</v>
+        <v>0.3118</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2036</v>
+        <v>0.1998</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5787</v>
+        <v>0.5988</v>
       </c>
       <c r="J39" t="n">
-        <v>0.316</v>
+        <v>0.3169</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2394</v>
+        <v>0.2422</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8177</v>
+        <v>0.8166</v>
       </c>
     </row>
     <row r="40">
@@ -2254,22 +2254,22 @@
         <v>48</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3358</v>
+        <v>0.3367</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2114</v>
+        <v>0.2122</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5314</v>
+        <v>0.5289</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3726</v>
+        <v>0.3776</v>
       </c>
       <c r="K40" t="n">
-        <v>0.279</v>
+        <v>0.2797</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7452</v>
+        <v>0.7383</v>
       </c>
     </row>
     <row r="41">
@@ -2300,22 +2300,22 @@
         <v>12</v>
       </c>
       <c r="G41" t="n">
-        <v>0.336</v>
+        <v>0.3296</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2085</v>
+        <v>0.2072</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5343</v>
+        <v>0.552</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3296</v>
+        <v>0.3082</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2431</v>
+        <v>0.2317</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8268</v>
       </c>
     </row>
     <row r="42">
@@ -2346,22 +2346,22 @@
         <v>24</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2837</v>
+        <v>0.2819</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1746</v>
+        <v>0.1758</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="J42" t="n">
-        <v>0.295</v>
+        <v>0.2901</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2207</v>
+        <v>0.219</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8409</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="43">
@@ -2392,22 +2392,22 @@
         <v>48</v>
       </c>
       <c r="G43" t="n">
-        <v>0.32</v>
+        <v>0.3131</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1997</v>
+        <v>0.196</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5734</v>
+        <v>0.5916</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3749</v>
+        <v>0.3776</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2751</v>
+        <v>0.277</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7416</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="44">
@@ -2438,22 +2438,22 @@
         <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2247</v>
+        <v>0.2209</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1419</v>
+        <v>0.1403</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7907</v>
+        <v>0.7977</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2657</v>
+        <v>0.2534</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1961</v>
+        <v>0.1861</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8709</v>
+        <v>0.8826000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2484,22 +2484,22 @@
         <v>24</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2243</v>
+        <v>0.2319</v>
       </c>
       <c r="H45" t="n">
-        <v>0.142</v>
+        <v>0.1437</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7906</v>
+        <v>0.7763</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2779</v>
+        <v>0.2681</v>
       </c>
       <c r="K45" t="n">
-        <v>0.2021</v>
+        <v>0.1978</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8683</v>
       </c>
     </row>
     <row r="46">
@@ -2530,22 +2530,22 @@
         <v>48</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2772</v>
+        <v>0.2742</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1781</v>
+        <v>0.1684</v>
       </c>
       <c r="I46" t="n">
-        <v>0.678</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3876</v>
+        <v>0.3671</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2774</v>
+        <v>0.2564</v>
       </c>
       <c r="L46" t="n">
-        <v>0.7232</v>
+        <v>0.7517</v>
       </c>
     </row>
     <row r="47">
@@ -2576,22 +2576,22 @@
         <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2076</v>
+        <v>0.2133</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1302</v>
+        <v>0.1301</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8194</v>
+        <v>0.8095</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2348</v>
+        <v>0.2473</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1657</v>
+        <v>0.1702</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.8875999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2622,22 +2622,22 @@
         <v>24</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2023</v>
+        <v>0.2021</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1285</v>
+        <v>0.129</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8279</v>
+        <v>0.8283</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2569</v>
+        <v>0.2431</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1816</v>
+        <v>0.1746</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8784</v>
+        <v>0.8911</v>
       </c>
     </row>
     <row r="49">
@@ -2668,22 +2668,22 @@
         <v>48</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2684</v>
+        <v>0.2608</v>
       </c>
       <c r="H49" t="n">
-        <v>0.167</v>
+        <v>0.1605</v>
       </c>
       <c r="I49" t="n">
-        <v>0.695</v>
+        <v>0.712</v>
       </c>
       <c r="J49" t="n">
-        <v>0.3923</v>
+        <v>0.348</v>
       </c>
       <c r="K49" t="n">
-        <v>0.2554</v>
+        <v>0.2415</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7149</v>
+        <v>0.7756999999999999</v>
       </c>
     </row>
   </sheetData>
